--- a/backend/sample_upload_1.xlsx
+++ b/backend/sample_upload_1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79D71E5-444F-3D40-A9D5-74F2F87B43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83F6EF6-FA93-5C4B-B8EA-A722CE2A8966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14800" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="19480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="218">
   <si>
     <t>Gender</t>
   </si>
@@ -658,6 +658,18 @@
   </si>
   <si>
     <t>fixed</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX5"/>
+  <dimension ref="A1:BX6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="76" width="24" customWidth="1"/>
@@ -1478,311 +1490,311 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:76" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="J3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>140</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="N3" t="s">
-        <v>140</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="P3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="R3" t="s">
-        <v>140</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="T3" t="s">
-        <v>140</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" t="s">
-        <v>140</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="X3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AK3" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AM3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AQ3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AS3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AU3" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AY3" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BC3" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BE3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BG3" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BK3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BM3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BO3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ3" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS3" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BU3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BW3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>140</v>
+    <row r="3" spans="1:76" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BP3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BS3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BT3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
         <v>140</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="F4" t="s">
         <v>140</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>140</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="J4" t="s">
         <v>140</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="s">
         <v>140</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="N4" t="s">
         <v>140</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="P4" t="s">
         <v>140</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="R4" t="s">
         <v>140</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="T4" t="s">
         <v>140</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V4" t="s">
         <v>140</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="X4" t="s">
         <v>140</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="s">
         <v>140</v>
@@ -1794,43 +1806,43 @@
         <v>140</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="AD4" t="s">
         <v>140</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="s">
         <v>140</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="AH4" t="s">
         <v>140</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="AJ4" t="s">
         <v>140</v>
       </c>
       <c r="AK4" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="AL4" t="s">
         <v>140</v>
       </c>
       <c r="AM4" s="4" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="AN4" t="s">
         <v>140</v>
       </c>
       <c r="AO4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="s">
         <v>140</v>
@@ -1842,37 +1854,37 @@
         <v>140</v>
       </c>
       <c r="AS4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AT4" t="s">
         <v>140</v>
       </c>
       <c r="AU4" s="4" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="AV4" t="s">
         <v>140</v>
       </c>
       <c r="AW4" s="4" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="AX4" t="s">
         <v>140</v>
       </c>
       <c r="AY4" s="4" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="AZ4" t="s">
         <v>140</v>
       </c>
       <c r="BA4" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="s">
         <v>140</v>
       </c>
       <c r="BC4" s="4" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="BD4" t="s">
         <v>140</v>
@@ -1884,25 +1896,25 @@
         <v>140</v>
       </c>
       <c r="BG4" s="4" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="BH4" t="s">
         <v>140</v>
       </c>
       <c r="BI4" s="4" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="BJ4" t="s">
         <v>140</v>
       </c>
       <c r="BK4" s="4" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="BL4" t="s">
         <v>140</v>
       </c>
       <c r="BM4" s="4" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="BN4" t="s">
         <v>140</v>
@@ -1914,25 +1926,25 @@
         <v>140</v>
       </c>
       <c r="BQ4" s="4" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="BR4" t="s">
         <v>140</v>
       </c>
       <c r="BS4" s="4" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="BT4" t="s">
         <v>140</v>
       </c>
       <c r="BU4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="BV4" t="s">
         <v>140</v>
       </c>
       <c r="BW4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BX4" t="s">
         <v>140</v>
@@ -1940,61 +1952,61 @@
     </row>
     <row r="5" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
         <v>140</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>140</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="J5" t="s">
         <v>140</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" t="s">
         <v>140</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N5" t="s">
         <v>140</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="P5" t="s">
         <v>140</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="R5" t="s">
         <v>140</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="T5" t="s">
         <v>140</v>
@@ -2006,7 +2018,7 @@
         <v>140</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="X5" t="s">
         <v>140</v>
@@ -2024,43 +2036,43 @@
         <v>140</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="AD5" t="s">
         <v>140</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="AF5" t="s">
         <v>140</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="AH5" t="s">
         <v>140</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="AJ5" t="s">
         <v>140</v>
       </c>
       <c r="AK5" s="4" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AL5" t="s">
         <v>140</v>
       </c>
       <c r="AM5" s="4" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="AN5" t="s">
         <v>140</v>
       </c>
       <c r="AO5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP5" t="s">
         <v>140</v>
@@ -2072,37 +2084,37 @@
         <v>140</v>
       </c>
       <c r="AS5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="s">
         <v>140</v>
       </c>
       <c r="AU5" s="4" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="AV5" t="s">
         <v>140</v>
       </c>
       <c r="AW5" s="4" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="AX5" t="s">
         <v>140</v>
       </c>
       <c r="AY5" s="4" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="AZ5" t="s">
         <v>140</v>
       </c>
       <c r="BA5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BB5" t="s">
         <v>140</v>
       </c>
       <c r="BC5" s="4" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="BD5" t="s">
         <v>140</v>
@@ -2114,13 +2126,13 @@
         <v>140</v>
       </c>
       <c r="BG5" s="4" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="BH5" t="s">
         <v>140</v>
       </c>
       <c r="BI5" s="4" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="BJ5" t="s">
         <v>140</v>
@@ -2132,7 +2144,7 @@
         <v>140</v>
       </c>
       <c r="BM5" s="4" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="BN5" t="s">
         <v>140</v>
@@ -2144,13 +2156,13 @@
         <v>140</v>
       </c>
       <c r="BQ5" s="4" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="BR5" t="s">
         <v>140</v>
       </c>
       <c r="BS5" s="4" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="BT5" t="s">
         <v>140</v>
@@ -2165,6 +2177,236 @@
         <v>57</v>
       </c>
       <c r="BX5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:76" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="N6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="P6" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="R6" t="s">
+        <v>140</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="T6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="V6" t="s">
+        <v>140</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="X6" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG6" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI6" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AU6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AW6" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY6" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC6" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BG6" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BK6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BM6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BO6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BQ6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BS6" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BU6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BW6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="BX6" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2176,12 +2418,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2219,7 +2461,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2257,7 +2499,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2295,7 +2537,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2327,7 +2569,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -2350,7 +2592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D6" t="s">
         <v>18</v>
       </c>
@@ -2370,7 +2612,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>19</v>
       </c>
@@ -2381,7 +2623,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>20</v>
       </c>
@@ -2392,12 +2634,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
         <v>3</v>
       </c>
